--- a/src/nodes/HPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-16.834681531024678</v>
+        <v>-16.851490058831406</v>
       </c>
       <c r="B1">
-        <v>10.213640497803118</v>
+        <v>10.185884216232465</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.234669960108391</v>
+        <v>-15.2905840909926</v>
       </c>
       <c r="B2">
-        <v>10.534024510881382</v>
+        <v>10.457587575307603</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-14.003458792257129</v>
+        <v>-14.073692953269978</v>
       </c>
       <c r="B3">
-        <v>10.36547301362234</v>
+        <v>10.271648042826611</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-12.830656156532065</v>
+        <v>-12.911746405029613</v>
       </c>
       <c r="B4">
-        <v>10.119486662101117</v>
+        <v>10.012615728858458</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-11.698959040209672</v>
+        <v>-11.788626097588113</v>
       </c>
       <c r="B5">
-        <v>9.81900484924147</v>
+        <v>9.70193287092554</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-10.6012850722635</v>
+        <v>-10.697732365271017</v>
       </c>
       <c r="B6">
-        <v>9.4734169972442341</v>
+        <v>9.348379003565789</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-9.53357502508993</v>
+        <v>-9.6352813144991174</v>
       </c>
       <c r="B7">
-        <v>9.0881046092299513</v>
+        <v>8.9569878400012257</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-8.4934259297533359</v>
+        <v>-8.5990316801349458</v>
       </c>
       <c r="B8">
-        <v>8.6662534106834634</v>
+        <v>8.53074093500351</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-7.4771098900380375</v>
+        <v>-7.585508662359616</v>
       </c>
       <c r="B9">
-        <v>8.21280564359678</v>
+        <v>8.0742608143985155</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.4806073020014141</v>
+        <v>-6.5909659683642987</v>
       </c>
       <c r="B10">
-        <v>7.7330902801963592</v>
+        <v>7.5925311711074714</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.5000566580731229</v>
+        <v>-5.6118048680617978</v>
       </c>
       <c r="B11">
-        <v>7.23222669713929</v>
+        <v>7.0903393953788658</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.5333838742976171</v>
+        <v>-4.6460914064832117</v>
       </c>
       <c r="B12">
-        <v>6.7129646020963305</v>
+        <v>6.5702582273001191</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.5855064648062607</v>
+        <v>-3.6984031664111647</v>
       </c>
       <c r="B13">
-        <v>6.1687846223622831</v>
+        <v>6.0261981089871437</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.6593571837461236</v>
+        <v>-2.7714694967534244</v>
       </c>
       <c r="B14">
-        <v>5.595798672041167</v>
+        <v>5.4545281878810785</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.7429381472401835</v>
+        <v>-1.8541152731667885</v>
       </c>
       <c r="B15">
-        <v>5.0099128928498073</v>
+        <v>4.8701147306954571</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.82524503218711931</v>
+        <v>-0.936090803545063</v>
       </c>
       <c r="B16">
-        <v>4.4257162176818481</v>
+        <v>4.2865929017383317</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>0.085821603387551543</v>
+        <v>-0.024752597981019149</v>
       </c>
       <c r="B17">
-        <v>3.832734516525357</v>
+        <v>3.6941763364233839</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.98005279263959688</v>
+        <v>0.87039285399844812</v>
       </c>
       <c r="B18">
-        <v>3.2174332965421528</v>
+        <v>3.080218552753986</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.8569108145767714</v>
+        <v>1.7488453473289152</v>
       </c>
       <c r="B19">
-        <v>2.57909967649464</v>
+        <v>2.4440541279866586</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.718275759669829</v>
+        <v>2.6123562480615763</v>
       </c>
       <c r="B20">
-        <v>1.9202261780453747</v>
+        <v>1.7880129041912074</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.5660277183895235</v>
+        <v>3.4626769222476264</v>
       </c>
       <c r="B21">
-        <v>1.2433053228569089</v>
+        <v>1.1144247234374389</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>4.4017112206541826</v>
+        <v>4.3012460833240285</v>
       </c>
       <c r="B22">
-        <v>0.55038476466707309</v>
+        <v>0.42520350605602614</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.22552855417244</v>
+        <v>5.1282518342708165</v>
       </c>
       <c r="B23">
-        <v>-0.15826731448519973</v>
+        <v>-0.27940051457889853</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6.0373464461004964</v>
+        <v>5.9435696254537875</v>
       </c>
       <c r="B24">
-        <v>-0.88282760048569253</v>
+        <v>-0.99955302683232827</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.8370316235945632</v>
+        <v>6.74707490723875</v>
       </c>
       <c r="B25">
-        <v>-1.6234727792201984</v>
+        <v>-1.7354197190692635</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.6243938916909544</v>
+        <v>7.5385899748233918</v>
       </c>
       <c r="B26">
-        <v>-2.3804550008242686</v>
+        <v>-2.4872369919691124</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.3990153669464878</v>
+        <v>8.317724502733018</v>
       </c>
       <c r="B27">
-        <v>-3.1543282724325734</v>
+        <v>-3.2555240954689695</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.1604212437980728</v>
+        <v>9.0840350103248113</v>
       </c>
       <c r="B28">
-        <v>-3.9457220654295355</v>
+        <v>-4.0408709918203263</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.9081367166826322</v>
+        <v>9.8370780169559655</v>
       </c>
       <c r="B29">
-        <v>-4.7552658511995842</v>
+        <v>-4.8438676432746908</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>10.641933413988079</v>
+        <v>10.576639392764919</v>
       </c>
       <c r="B30">
-        <v>-5.5832623924018021</v>
+        <v>-5.6647989067638846</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>11.362568699906291</v>
+        <v>11.303422411015131</v>
       </c>
       <c r="B31">
-        <v>-6.428707616793881</v>
+        <v>-6.5027292179410683</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>12.071046372580147</v>
+        <v>12.018359695751309</v>
       </c>
       <c r="B32">
-        <v>-7.290270743408171</v>
+        <v>-7.3564179071397291</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>12.76837023015252</v>
+        <v>12.722383871018167</v>
       </c>
       <c r="B33">
-        <v>-8.1666209912770142</v>
+        <v>-8.2246243046933536</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>13.455140189288729</v>
+        <v>13.416051258870557</v>
       </c>
       <c r="B34">
-        <v>-9.05696302352312</v>
+        <v>-9.1066083354321172</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>14.130340640743874</v>
+        <v>14.09841297340393</v>
       </c>
       <c r="B35">
-        <v>-9.9626432796306457</v>
+        <v>-10.003632302172933</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>14.792552093795502</v>
+        <v>14.768143826723874</v>
       </c>
       <c r="B36">
-        <v>-10.885543643174103</v>
+        <v>-10.917459102229408</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>15.440355057721149</v>
+        <v>15.423918630935983</v>
       </c>
       <c r="B37">
-        <v>-11.827545997728011</v>
+        <v>-11.849851632915147</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>16.071342974022343</v>
+        <v>16.063492781766715</v>
       </c>
       <c r="B38">
-        <v>-12.791840827624361</v>
+        <v>-12.803795891054174</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>16.679161013096518</v>
+        <v>16.680944009425989</v>
       </c>
       <c r="B39">
-        <v>-13.786853020225022</v>
+        <v>-13.787170271512171</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>17.256467277565086</v>
+        <v>17.269430627744594</v>
       </c>
       <c r="B40">
-        <v>-14.822316063649353</v>
+        <v>-14.809076268665251</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>17.795919870049453</v>
+        <v>17.8221109505533</v>
       </c>
       <c r="B41">
-        <v>-15.907963446016682</v>
+        <v>-15.878615376889508</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>17.795919870049453</v>
+        <v>17.8221109505533</v>
       </c>
       <c r="B42">
-        <v>-15.907963446016682</v>
+        <v>-15.878615376889508</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>16.912533718126781</v>
+        <v>16.949127719468645</v>
       </c>
       <c r="B43">
-        <v>-15.278284465550595</v>
+        <v>-15.235175193143991</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>16.05036176296089</v>
+        <v>16.0953476841674</v>
       </c>
       <c r="B44">
-        <v>-14.620480857151678</v>
+        <v>-14.566189000110217</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>15.202189246309661</v>
+        <v>15.254056019678389</v>
       </c>
       <c r="B45">
-        <v>-13.944117554789</v>
+        <v>-13.8805895287262</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>14.360801409930964</v>
+        <v>14.418537901030408</v>
       </c>
       <c r="B46">
-        <v>-13.258759492431604</v>
+        <v>-13.187309509929941</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>13.519965539615425</v>
+        <v>13.582992906870517</v>
       </c>
       <c r="B47">
-        <v>-12.572669663496578</v>
+        <v>-12.494065243624293</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>12.677377097284689</v>
+        <v>12.7452782303188</v>
       </c>
       <c r="B48">
-        <v>-11.888903299193187</v>
+        <v>-11.803707305571464</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>11.831713588893162</v>
+        <v>11.9041654681136</v>
       </c>
       <c r="B49">
-        <v>-11.209213690178721</v>
+        <v>-11.117869840498507</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.981652520395244</v>
+        <v>11.05842621699326</v>
       </c>
       <c r="B50">
-        <v>-10.535354127110486</v>
+        <v>-10.438186993132474</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>10.126270167854523</v>
+        <v>10.207203275491544</v>
       </c>
       <c r="B51">
-        <v>-9.8685492329295279</v>
+        <v>-9.765799098491831</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>9.2662378877713039</v>
+        <v>9.35112424932392</v>
       </c>
       <c r="B52">
-        <v>-9.2079089597119044</v>
+        <v>-9.0998712527607015</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8.4026258067550827</v>
+        <v>8.49118794600127</v>
       </c>
       <c r="B53">
-        <v>-8.5520145918174286</v>
+        <v>-8.4390747424146255</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>7.5365040514153474</v>
+        <v>7.6283931730344845</v>
       </c>
       <c r="B54">
-        <v>-7.8994474136059072</v>
+        <v>-7.7820808539291422</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.6686917616637853</v>
+        <v>6.7635048443591312</v>
       </c>
       <c r="B55">
-        <v>-7.2491214539465281</v>
+        <v>-7.1278720223779111</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.7990041306208866</v>
+        <v>5.8963522996095179</v>
       </c>
       <c r="B56">
-        <v>-6.6012817197460079</v>
+        <v>-6.4766752772270966</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.9270053647093341</v>
+        <v>5.0265309848446229</v>
       </c>
       <c r="B57">
-        <v>-5.9565059624204348</v>
+        <v>-5.8290287965409791</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.0522596703518232</v>
+        <v>4.1536363461234407</v>
       </c>
       <c r="B58">
-        <v>-5.315371933385908</v>
+        <v>-5.1854707583838486</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.1743838466968959</v>
+        <v>3.2773126647435067</v>
       </c>
       <c r="B59">
-        <v>-4.6783876594837741</v>
+        <v>-4.5464743753073567</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.2932050637966146</v>
+        <v>2.3973995629566573</v>
       </c>
       <c r="B60">
-        <v>-4.0457822692564687</v>
+        <v>-3.9122529978126837</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.4086030844289013</v>
+        <v>1.5137854982532792</v>
       </c>
       <c r="B61">
-        <v>-3.4177151666716861</v>
+        <v>-3.2829550108883776</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.52045767137168542</v>
+        <v>0.62635892812376859</v>
       </c>
       <c r="B62">
-        <v>-2.7943457556971256</v>
+        <v>-2.6587287995229958</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.3710202845920641</v>
+        <v>-0.26468346018465527</v>
       </c>
       <c r="B63">
-        <v>-2.1753944488059269</v>
+        <v>-2.0393127106926809</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.2642953806591966</v>
+        <v>-1.1579120603974518</v>
       </c>
       <c r="B64">
-        <v>-1.5588256924930164</v>
+        <v>-1.4228049393239521</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.1575010860215156</v>
+        <v>-2.05158903648325</v>
       </c>
       <c r="B65">
-        <v>-0.942164941758763</v>
+        <v>-0.80689364233092165</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.048770869870824</v>
+        <v>-2.9439765524106796</v>
       </c>
       <c r="B66">
-        <v>-0.322937651603538</v>
+        <v>-0.18926697662770253</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.9386596122793294</v>
+        <v>-3.83559193481272</v>
       </c>
       <c r="B67">
-        <v>0.29812054816036454</v>
+        <v>0.42938685822141442</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.8374078368408524</v>
+        <v>-4.73597316097975</v>
       </c>
       <c r="B68">
-        <v>0.90743332847296154</v>
+        <v>1.0363794920514242</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.75295290523402</v>
+        <v>-5.6525134642013057</v>
       </c>
       <c r="B69">
-        <v>1.4944777670412777</v>
+        <v>1.6218757074112962</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.674333887955064</v>
+        <v>-6.5750064511061517</v>
       </c>
       <c r="B70">
-        <v>2.0737852678880695</v>
+        <v>2.1994530683066036</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.5896003856148786</v>
+        <v>-7.492324378033322</v>
       </c>
       <c r="B71">
-        <v>2.6611990203794327</v>
+        <v>2.783914810934415</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.5017424104653436</v>
+        <v>-8.40725372682364</v>
       </c>
       <c r="B72">
-        <v>3.25275502893906</v>
+        <v>3.3715540788011449</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-9.41573951995814</v>
+        <v>-9.324433987947355</v>
       </c>
       <c r="B73">
-        <v>3.8418516672030454</v>
+        <v>3.9561989582325023</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-10.32958904070316</v>
+        <v>-10.242002460890607</v>
       </c>
       <c r="B74">
-        <v>4.4311439705994848</v>
+        <v>4.5403273995220257</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-11.239505688011503</v>
+        <v>-11.156436471817058</v>
       </c>
       <c r="B75">
-        <v>5.0256502636360452</v>
+        <v>5.1286256152958574</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-12.141555962840897</v>
+        <v>-12.064075644584595</v>
       </c>
       <c r="B76">
-        <v>5.6305853653467084</v>
+        <v>5.7259630035427209</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.032103256225287</v>
+        <v>-12.9615362670612</v>
       </c>
       <c r="B77">
-        <v>6.25077049405429</v>
+        <v>6.3368409161484278</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-13.908846733856827</v>
+        <v>-13.846678985461024</v>
       </c>
       <c r="B78">
-        <v>6.8892559707105994</v>
+        <v>6.9641053352245272</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-14.767834305005742</v>
+        <v>-14.715826808867144</v>
       </c>
       <c r="B79">
-        <v>7.5512812621974614</v>
+        <v>7.6126477613928873</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-15.602100953618901</v>
+        <v>-15.562497170029104</v>
       </c>
       <c r="B80">
-        <v>8.246080207876604</v>
+        <v>8.2910919531705574</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-16.394469175213992</v>
+        <v>-16.370696954131574</v>
       </c>
       <c r="B81">
-        <v>8.99642580867369</v>
+        <v>9.0207135494787</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-16.834681531024678</v>
+        <v>-16.851490058831406</v>
       </c>
       <c r="B82">
-        <v>10.213640497803118</v>
+        <v>10.185884216232465</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-21.238829006231281</v>
+        <v>-21.17318662901409</v>
       </c>
       <c r="B1">
-        <v>8.1722751980626782</v>
+        <v>8.3408697053568783</v>
       </c>
       <c r="C1">
         <v>228.43351223002802</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-19.849655816367758</v>
+        <v>-19.835884467918635</v>
       </c>
       <c r="B2">
-        <v>8.2114300106066374</v>
+        <v>8.2515037168123317</v>
       </c>
       <c r="C2">
         <v>228.43351223002802</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-18.57835333339499</v>
+        <v>-18.586196431376706</v>
       </c>
       <c r="B3">
-        <v>7.9792066607368515</v>
+        <v>7.9647304667643981</v>
       </c>
       <c r="C3">
         <v>228.43351223002802</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-17.325641067559157</v>
+        <v>-17.350929032006118</v>
       </c>
       <c r="B4">
-        <v>7.7041823546450141</v>
+        <v>7.6454654409025107</v>
       </c>
       <c r="C4">
         <v>228.43351223002802</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-16.086000250691789</v>
+        <v>-16.126012721342878</v>
       </c>
       <c r="B5">
-        <v>7.3990631598847463</v>
+        <v>7.30287791897381</v>
       </c>
       <c r="C5">
         <v>228.43351223002802</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-14.857180715961242</v>
+        <v>-14.909787712490266</v>
       </c>
       <c r="B6">
-        <v>7.0690297201970029</v>
+        <v>6.9407076402912518</v>
       </c>
       <c r="C6">
         <v>228.43351223002802</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-13.637898049397055</v>
+        <v>-13.701306268456664</v>
       </c>
       <c r="B7">
-        <v>6.7170391901817279</v>
+        <v>6.5610899930138924</v>
       </c>
       <c r="C7">
         <v>228.43351223002802</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-12.427397018401855</v>
+        <v>-12.500010814733054</v>
       </c>
       <c r="B8">
-        <v>6.3448303702574451</v>
+        <v>6.16528127294418</v>
       </c>
       <c r="C8">
         <v>228.43351223002802</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-11.224497064732299</v>
+        <v>-11.30503029046584</v>
       </c>
       <c r="B9">
-        <v>5.9551213040767994</v>
+        <v>5.7552441058412152</v>
       </c>
       <c r="C9">
         <v>228.43351223002802</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-10.027923612530325</v>
+        <v>-10.115424359488994</v>
       </c>
       <c r="B10">
-        <v>5.5508464955835208</v>
+        <v>5.3330972047364282</v>
       </c>
       <c r="C10">
         <v>228.43351223002802</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.8364513411248211</v>
+        <v>-8.93028907073127</v>
       </c>
       <c r="B11">
-        <v>5.1348270466515444</v>
+        <v>4.9008773017939156</v>
       </c>
       <c r="C11">
         <v>228.43351223002802</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.6494261082769057</v>
+        <v>-7.7491415985538152</v>
       </c>
       <c r="B12">
-        <v>4.708569013564305</v>
+        <v>4.4596722728286187</v>
       </c>
       <c r="C12">
         <v>228.43351223002802</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.4684292302895923</v>
+        <v>-6.5731472339525663</v>
       </c>
       <c r="B13">
-        <v>4.268431672313036</v>
+        <v>4.0068565491262014</v>
       </c>
       <c r="C13">
         <v>228.43351223002802</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.2944064393193235</v>
+        <v>-5.4030027337730369</v>
       </c>
       <c r="B14">
-        <v>3.812237628178397</v>
+        <v>3.5408602370022071</v>
       </c>
       <c r="C14">
         <v>228.43351223002802</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.1235256723942983</v>
+        <v>-4.23588260162426</v>
       </c>
       <c r="B15">
-        <v>3.3488095838909508</v>
+        <v>3.0680495874209517</v>
       </c>
       <c r="C15">
         <v>228.43351223002802</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.9522721804310419</v>
+        <v>-3.0691953065680488</v>
       </c>
       <c r="B16">
-        <v>2.8862396784798197</v>
+        <v>2.5942636934307011</v>
       </c>
       <c r="C16">
         <v>228.43351223002802</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.7831782650275367</v>
+        <v>-1.9048074327137312</v>
       </c>
       <c r="B17">
-        <v>2.418697698718431</v>
+        <v>2.1152968717667173</v>
       </c>
       <c r="C17">
         <v>228.43351223002802</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.61951403041138942</v>
+        <v>-0.74512953650805369</v>
       </c>
       <c r="B18">
-        <v>1.9386547606321647</v>
+        <v>1.6257177910166831</v>
       </c>
       <c r="C18">
         <v>228.43351223002802</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.53854625935283762</v>
+        <v>0.40971005130014593</v>
       </c>
       <c r="B19">
-        <v>1.4457096495098816</v>
+        <v>1.1252373034909475</v>
       </c>
       <c r="C19">
         <v>228.43351223002802</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.6916023002413392</v>
+        <v>1.5601535563865057</v>
       </c>
       <c r="B20">
-        <v>0.941243067956314</v>
+        <v>0.61485180743052781</v>
       </c>
       <c r="C20">
         <v>228.43351223002802</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.8402537882303007</v>
+        <v>2.7066432044266544</v>
       </c>
       <c r="B21">
-        <v>0.426635718576199</v>
+        <v>0.095557701076446483</v>
       </c>
       <c r="C21">
         <v>228.43351223002802</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.9849936474525585</v>
+        <v>3.8495424690501827</v>
       </c>
       <c r="B22">
-        <v>-0.096977520857139149</v>
+        <v>-0.43182605705050381</v>
       </c>
       <c r="C22">
         <v>228.43351223002802</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.12588771466749</v>
+        <v>4.9888998157024744</v>
       </c>
       <c r="B23">
-        <v>-0.62944507189598908</v>
+        <v>-0.96719026731041657</v>
       </c>
       <c r="C23">
         <v>228.43351223002802</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6.2628950547911222</v>
+        <v>6.1246849577828737</v>
       </c>
       <c r="B24">
-        <v>-1.1708611809240523</v>
+        <v>-1.5106031697836153</v>
       </c>
       <c r="C24">
         <v>228.43351223002802</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>7.3959747327394734</v>
+        <v>7.256867608690718</v>
       </c>
       <c r="B25">
-        <v>-1.7213200943250242</v>
+        <v>-2.0621330045504176</v>
       </c>
       <c r="C25">
         <v>228.43351223002802</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>8.5250681698743254</v>
+        <v>8.3854044390865869</v>
       </c>
       <c r="B26">
-        <v>-2.2809566799012151</v>
+        <v>-2.6218773988630475</v>
       </c>
       <c r="C26">
         <v>228.43351223002802</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>9.6500462133405218</v>
+        <v>9.5101999486760622</v>
       </c>
       <c r="B27">
-        <v>-2.8500682911294053</v>
+        <v>-3.1900515286613675</v>
       </c>
       <c r="C27">
         <v>228.43351223002802</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>10.770762066728672</v>
+        <v>10.631145594425966</v>
       </c>
       <c r="B28">
-        <v>-3.4289929029049846</v>
+        <v>-3.7668999570571433</v>
       </c>
       <c r="C28">
         <v>228.43351223002802</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>11.887068933629369</v>
+        <v>11.748132833303108</v>
       </c>
       <c r="B29">
-        <v>-4.0180684901233388</v>
+        <v>-4.3526672471621337</v>
       </c>
       <c r="C29">
         <v>228.43351223002802</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.998899455886111</v>
+        <v>12.861111650665368</v>
       </c>
       <c r="B30">
-        <v>-4.617450134002004</v>
+        <v>-4.9474660891799713</v>
       </c>
       <c r="C30">
         <v>228.43351223002802</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>14.106504028353953</v>
+        <v>13.970266145434849</v>
       </c>
       <c r="B31">
-        <v>-5.226561341047085</v>
+        <v>-5.5508816816817506</v>
       </c>
       <c r="C31">
         <v>228.43351223002802</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>15.21021248414085</v>
+        <v>15.075838944924701</v>
       </c>
       <c r="B32">
-        <v>-5.8446427240868326</v>
+        <v>-6.1623673503304284</v>
       </c>
       <c r="C32">
         <v>228.43351223002802</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>16.310354656354747</v>
+        <v>16.178072676448085</v>
       </c>
       <c r="B33">
-        <v>-6.4709348959494966</v>
+        <v>-6.7813764207889644</v>
       </c>
       <c r="C33">
         <v>228.43351223002802</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>17.407131855607766</v>
+        <v>17.27711517935839</v>
       </c>
       <c r="B34">
-        <v>-7.1049743716400711</v>
+        <v>-7.4075757896674075</v>
       </c>
       <c r="C34">
         <v>228.43351223002802</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>18.500231302528775</v>
+        <v>18.372735141169965</v>
       </c>
       <c r="B35">
-        <v>-7.7474812748705473</v>
+        <v>-8.04148663736419</v>
       </c>
       <c r="C35">
         <v>228.43351223002802</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>19.589211695250807</v>
+        <v>19.464606461437413</v>
       </c>
       <c r="B36">
-        <v>-8.3994716315296643</v>
+        <v>-8.6838437152248442</v>
       </c>
       <c r="C36">
         <v>228.43351223002802</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>20.673631731906912</v>
+        <v>20.552403039715315</v>
       </c>
       <c r="B37">
-        <v>-9.0619614675061619</v>
+        <v>-9.3353817745948913</v>
       </c>
       <c r="C37">
         <v>228.43351223002802</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>21.752735017920305</v>
+        <v>21.63556644615262</v>
       </c>
       <c r="B38">
-        <v>-9.7366922584874551</v>
+        <v>-9.9973590384857864</v>
       </c>
       <c r="C38">
         <v>228.43351223002802</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>22.824504787874883</v>
+        <v>22.712608933275604</v>
       </c>
       <c r="B39">
-        <v>-10.428307279355616</v>
+        <v>-10.673127616572643</v>
       </c>
       <c r="C39">
         <v>228.43351223002802</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>23.886609183644726</v>
+        <v>23.781810424204906</v>
       </c>
       <c r="B40">
-        <v>-11.142175254791402</v>
+        <v>-11.366563090196507</v>
       </c>
       <c r="C40">
         <v>228.43351223002802</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>24.936716347103921</v>
+        <v>24.84145084206115</v>
       </c>
       <c r="B41">
-        <v>-11.883664909475565</v>
+        <v>-12.081541040698426</v>
       </c>
       <c r="C41">
         <v>228.43351223002802</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>24.936716347103921</v>
+        <v>24.84145084206115</v>
       </c>
       <c r="B42">
-        <v>-11.883664909475565</v>
+        <v>-12.081541040698426</v>
       </c>
       <c r="C42">
         <v>228.43351223002802</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>23.776580353295738</v>
+        <v>23.700693953792722</v>
       </c>
       <c r="B43">
-        <v>-11.395498769855372</v>
+        <v>-11.549330199592284</v>
       </c>
       <c r="C43">
         <v>228.43351223002802</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>22.623343708596277</v>
+        <v>22.564307104712761</v>
       </c>
       <c r="B44">
-        <v>-10.891447999249568</v>
+        <v>-11.007273029789099</v>
       </c>
       <c r="C44">
         <v>228.43351223002802</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>21.474681407188431</v>
+        <v>21.430577195459016</v>
       </c>
       <c r="B45">
-        <v>-10.376865546010519</v>
+        <v>-10.459229391277292</v>
       </c>
       <c r="C45">
         <v>228.43351223002802</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>20.3282684432551</v>
+        <v>20.297791126669232</v>
       </c>
       <c r="B46">
-        <v>-9.8571043584905951</v>
+        <v>-9.909059144045278</v>
       </c>
       <c r="C46">
         <v>228.43351223002802</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>19.182094662813043</v>
+        <v>19.164467883109452</v>
       </c>
       <c r="B47">
-        <v>-9.3367924898213914</v>
+        <v>-9.360099229060916</v>
       </c>
       <c r="C47">
         <v>228.43351223002802</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>18.035409319214263</v>
+        <v>18.030054786058745</v>
       </c>
       <c r="B48">
-        <v>-8.8176584122513653</v>
+        <v>-8.8135949112097709</v>
       </c>
       <c r="C48">
         <v>228.43351223002802</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>16.8877765176446</v>
+        <v>16.894231240924466</v>
       </c>
       <c r="B49">
-        <v>-8.3007057028081928</v>
+        <v>-8.2702685363568431</v>
       </c>
       <c r="C49">
         <v>228.43351223002802</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>15.738760363289909</v>
+        <v>15.75667665311398</v>
       </c>
       <c r="B50">
-        <v>-7.78693793851955</v>
+        <v>-7.73084245036713</v>
       </c>
       <c r="C50">
         <v>228.43351223002802</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>14.588053217548882</v>
+        <v>14.617164944845806</v>
       </c>
       <c r="B51">
-        <v>-7.2770634073096163</v>
+        <v>-7.1958260390954152</v>
       </c>
       <c r="C51">
         <v>228.43351223002802</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>13.435860466671723</v>
+        <v>13.475848105583188</v>
       </c>
       <c r="B52">
-        <v>-6.7706092406885858</v>
+        <v>-6.6648768483556031</v>
       </c>
       <c r="C52">
         <v>228.43351223002802</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>12.282515753121478</v>
+        <v>12.332972641600536</v>
       </c>
       <c r="B53">
-        <v>-6.2668072810631532</v>
+        <v>-6.1374394639513756</v>
       </c>
       <c r="C53">
         <v>228.43351223002802</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>11.128352719361198</v>
+        <v>11.188785059172261</v>
       </c>
       <c r="B54">
-        <v>-5.7648893708400095</v>
+        <v>-5.612958471686416</v>
       </c>
       <c r="C54">
         <v>228.43351223002802</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.9736253147552141</v>
+        <v>10.043473076679231</v>
       </c>
       <c r="B55">
-        <v>-5.2642708328448489</v>
+        <v>-5.0910109149690683</v>
       </c>
       <c r="C55">
         <v>228.43351223002802</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.81826871627297</v>
+        <v>8.89698926092817</v>
       </c>
       <c r="B56">
-        <v>-4.7651009115793617</v>
+        <v>-4.5717036676263154</v>
       </c>
       <c r="C56">
         <v>228.43351223002802</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.6621384077852</v>
+        <v>7.74922739083227</v>
       </c>
       <c r="B57">
-        <v>-4.26771233196424</v>
+        <v>-4.0552760610898089</v>
       </c>
       <c r="C57">
         <v>228.43351223002802</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6.5050898731626257</v>
+        <v>6.60008124530472</v>
       </c>
       <c r="B58">
-        <v>-3.7724378189201735</v>
+        <v>-3.5419674267911949</v>
       </c>
       <c r="C58">
         <v>228.43351223002802</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.34699598794889</v>
+        <v>5.4494573895136558</v>
       </c>
       <c r="B59">
-        <v>-3.2795700558650442</v>
+        <v>-3.0319882868851877</v>
       </c>
       <c r="C59">
         <v>228.43351223002802</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.1877991943793624</v>
+        <v>4.2973135336470838</v>
       </c>
       <c r="B60">
-        <v>-2.7892415602055292</v>
+        <v>-2.5254339264188004</v>
       </c>
       <c r="C60">
         <v>228.43351223002802</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.0274593263623353</v>
+        <v>3.1436201741479661</v>
       </c>
       <c r="B61">
-        <v>-2.3015448078455</v>
+        <v>-2.0223708211621161</v>
       </c>
       <c r="C61">
         <v>228.43351223002802</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.865936217806093</v>
+        <v>1.9883478074592571</v>
       </c>
       <c r="B62">
-        <v>-1.8165722746888253</v>
+        <v>-1.5228654468852139</v>
       </c>
       <c r="C62">
         <v>228.43351223002802</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.70329621313831814</v>
+        <v>0.83154541597097509</v>
       </c>
       <c r="B63">
-        <v>-1.3341712134639907</v>
+        <v>-1.0268074391973845</v>
       </c>
       <c r="C63">
         <v>228.43351223002802</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.459968301135773</v>
+        <v>-0.32642407413866675</v>
       </c>
       <c r="B64">
-        <v>-0.85320798419793</v>
+        <v>-0.53337907306473109</v>
       </c>
       <c r="C64">
         <v>228.43351223002802</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.6232584279915641</v>
+        <v>-1.4851192507443918</v>
       </c>
       <c r="B65">
-        <v>-0.37230372374219373</v>
+        <v>-0.041585783292568408</v>
       </c>
       <c r="C65">
         <v>228.43351223002802</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.7859752704044487</v>
+        <v>-2.6440987017209334</v>
       </c>
       <c r="B66">
-        <v>0.10992043105167082</v>
+        <v>0.4495669953137934</v>
       </c>
       <c r="C66">
         <v>228.43351223002802</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.9482941016372366</v>
+        <v>-3.8034917854558712</v>
       </c>
       <c r="B67">
-        <v>0.59306094195745807</v>
+        <v>0.9397877996463887</v>
       </c>
       <c r="C67">
         <v>228.43351223002802</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.1134868761023862</v>
+        <v>-4.96571094238817</v>
       </c>
       <c r="B68">
-        <v>1.0695846652503247</v>
+        <v>1.4236410533866246</v>
       </c>
       <c r="C68">
         <v>228.43351223002802</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.2840880492321229</v>
+        <v>-6.1326249498171705</v>
       </c>
       <c r="B69">
-        <v>1.5336564288501371</v>
+        <v>1.8969161316963139</v>
       </c>
       <c r="C69">
         <v>228.43351223002802</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.4565853993880014</v>
+        <v>-7.3016448504322629</v>
       </c>
       <c r="B70">
-        <v>1.9933625527542098</v>
+        <v>2.3654463288694902</v>
       </c>
       <c r="C70">
         <v>228.43351223002802</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-8.6271496214539258</v>
+        <v>-8.4699479560908912</v>
       </c>
       <c r="B71">
-        <v>2.4575193901782257</v>
+        <v>2.83559156848174</v>
       </c>
       <c r="C71">
         <v>228.43351223002802</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-9.7967297534737519</v>
+        <v>-9.6382343899325651</v>
       </c>
       <c r="B72">
-        <v>2.9239419351338545</v>
+        <v>3.3057743721025963</v>
       </c>
       <c r="C72">
         <v>228.43351223002802</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-10.966910681395685</v>
+        <v>-10.807673077824473</v>
       </c>
       <c r="B73">
-        <v>3.388981245083944</v>
+        <v>3.773360981128437</v>
       </c>
       <c r="C73">
         <v>228.43351223002802</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-12.137042339625291</v>
+        <v>-11.977785345262394</v>
       </c>
       <c r="B74">
-        <v>3.8541339905000465</v>
+        <v>4.239429918269054</v>
       </c>
       <c r="C74">
         <v>228.43351223002802</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-13.305903740280421</v>
+        <v>-13.147671653134591</v>
       </c>
       <c r="B75">
-        <v>4.3222112977131166</v>
+        <v>4.7060079749073251</v>
       </c>
       <c r="C75">
         <v>228.43351223002802</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-14.472225157870648</v>
+        <v>-14.316396604270654</v>
       </c>
       <c r="B76">
-        <v>4.7961365034829839</v>
+        <v>5.1752027358050592</v>
       </c>
       <c r="C76">
         <v>228.43351223002802</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-15.634831149402992</v>
+        <v>-15.483094346535372</v>
       </c>
       <c r="B77">
-        <v>5.2786158744289979</v>
+        <v>5.6489650907274784</v>
       </c>
       <c r="C77">
         <v>228.43351223002802</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-16.792972139482512</v>
+        <v>-16.647213065992954</v>
       </c>
       <c r="B78">
-        <v>5.77137518617968</v>
+        <v>6.1285383560744995</v>
       </c>
       <c r="C78">
         <v>228.43351223002802</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-17.94536961688209</v>
+        <v>-17.80781103625257</v>
       </c>
       <c r="B79">
-        <v>6.2773580032269569</v>
+        <v>6.6160443772546031</v>
       </c>
       <c r="C79">
         <v>228.43351223002802</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-19.089779806137216</v>
+        <v>-18.963234978570377</v>
       </c>
       <c r="B80">
-        <v>6.8017302542268041</v>
+        <v>7.1152082297734074</v>
       </c>
       <c r="C80">
         <v>228.43351223002802</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-20.220690708357218</v>
+        <v>-20.1094222374513</v>
       </c>
       <c r="B81">
-        <v>7.3571824215699362</v>
+        <v>7.6351836625247493</v>
       </c>
       <c r="C81">
         <v>228.43351223002802</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-21.238829006231281</v>
+        <v>-21.17318662901409</v>
       </c>
       <c r="B82">
-        <v>8.1722751980626782</v>
+        <v>8.3408697053568783</v>
       </c>
       <c r="C82">
         <v>228.43351223002802</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-24.398216592835812</v>
+        <v>-24.310454488322321</v>
       </c>
       <c r="B1">
-        <v>7.3291989134470876</v>
+        <v>7.6152434100961033</v>
       </c>
       <c r="C1">
         <v>258.22826917492205</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-22.93634240364656</v>
+        <v>-22.883049441083898</v>
       </c>
       <c r="B2">
-        <v>7.2637230560120543</v>
+        <v>7.4338383922652218</v>
       </c>
       <c r="C2">
         <v>258.22826917492205</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-21.536227675828716</v>
+        <v>-21.498730742538921</v>
       </c>
       <c r="B3">
-        <v>7.00946347269068</v>
+        <v>7.1257820943713854</v>
       </c>
       <c r="C3">
         <v>258.22826917492205</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-20.145797219492884</v>
+        <v>-20.121537432966822</v>
       </c>
       <c r="B4">
-        <v>6.7256014153147641</v>
+        <v>6.7967808878991356</v>
       </c>
       <c r="C4">
         <v>258.22826917492205</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-18.76215744700999</v>
+        <v>-18.749471141060766</v>
       </c>
       <c r="B5">
-        <v>6.4209818809368571</v>
+        <v>6.4527089369799624</v>
       </c>
       <c r="C5">
         <v>258.22826917492205</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-17.38412921059205</v>
+        <v>-17.381717420112203</v>
       </c>
       <c r="B6">
-        <v>6.099209238957874</v>
+        <v>6.0959602880185724</v>
       </c>
       <c r="C6">
         <v>258.22826917492205</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-16.011039848551491</v>
+        <v>-16.017811593226547</v>
       </c>
       <c r="B7">
-        <v>5.7623396533536946</v>
+        <v>5.72790084750969</v>
       </c>
       <c r="C7">
         <v>258.22826917492205</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-14.64249423085389</v>
+        <v>-14.657480641082342</v>
       </c>
       <c r="B8">
-        <v>5.4115809410069717</v>
+        <v>5.3493331491465446</v>
       </c>
       <c r="C8">
         <v>258.22826917492205</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-13.277874029284593</v>
+        <v>-13.300297428980974</v>
       </c>
       <c r="B9">
-        <v>5.0488231816171023</v>
+        <v>4.9615127450466705</v>
       </c>
       <c r="C9">
         <v>258.22826917492205</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-11.916511551753754</v>
+        <v>-11.94580074119963</v>
       </c>
       <c r="B10">
-        <v>4.6761073483024758</v>
+        <v>4.5657953676740686</v>
       </c>
       <c r="C10">
         <v>258.22826917492205</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-10.557764848851027</v>
+        <v>-10.593547153295882</v>
       </c>
       <c r="B11">
-        <v>4.295395725040712</v>
+        <v>4.163484452454302</v>
       </c>
       <c r="C11">
         <v>258.22826917492205</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-9.2012915302438625</v>
+        <v>-9.2433001099218046</v>
       </c>
       <c r="B12">
-        <v>3.9077349162103188</v>
+        <v>3.7552753481121517</v>
       </c>
       <c r="C12">
         <v>258.22826917492205</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-7.8479216992314251</v>
+        <v>-7.89563274082717</v>
       </c>
       <c r="B13">
-        <v>3.5105874969341127</v>
+        <v>3.3394833536077169</v>
       </c>
       <c r="C13">
         <v>258.22826917492205</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-6.4981520229419765</v>
+        <v>-6.5508879273854408</v>
       </c>
       <c r="B14">
-        <v>3.1024352760083924</v>
+        <v>2.9151005774353</v>
       </c>
       <c r="C14">
         <v>258.22826917492205</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.1499729301885173</v>
+        <v>-5.2076778723672419</v>
       </c>
       <c r="B15">
-        <v>2.6894210261790872</v>
+        <v>2.48620641599071</v>
       </c>
       <c r="C15">
         <v>258.22826917492205</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.8015412518263689</v>
+        <v>-3.8647296947759422</v>
       </c>
       <c r="B16">
-        <v>2.277178869422738</v>
+        <v>2.056542472182521</v>
       </c>
       <c r="C16">
         <v>258.22826917492205</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.4541856651953693</v>
+        <v>-2.5229608571487381</v>
       </c>
       <c r="B17">
-        <v>1.8616473606886996</v>
+        <v>1.6234118870688514</v>
       </c>
       <c r="C17">
         <v>258.22826917492205</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.109621799329334</v>
+        <v>-1.1835560419301605</v>
       </c>
       <c r="B18">
-        <v>1.4375822372510925</v>
+        <v>1.1833323152522286</v>
       </c>
       <c r="C18">
         <v>258.22826917492205</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.23205875644662768</v>
+        <v>0.15342153233984571</v>
       </c>
       <c r="B19">
-        <v>1.0047035327102483</v>
+        <v>0.73611792736324322</v>
       </c>
       <c r="C19">
         <v>258.22826917492205</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.5711704227345895</v>
+        <v>1.4881890130974869</v>
       </c>
       <c r="B20">
-        <v>0.56397235474804974</v>
+        <v>0.28240702303949755</v>
       </c>
       <c r="C20">
         <v>258.22826917492205</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.9080276201366031</v>
+        <v>2.8209635477789483</v>
       </c>
       <c r="B21">
-        <v>0.11634981104638638</v>
+        <v>-0.177162098081397</v>
       </c>
       <c r="C21">
         <v>258.22826917492205</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>4.2428888101328006</v>
+        <v>4.15192363351498</v>
       </c>
       <c r="B22">
-        <v>-0.3373740442049577</v>
+        <v>-0.64206474800007751</v>
       </c>
       <c r="C22">
         <v>258.22826917492205</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.5757886177155314</v>
+        <v>5.4810931662144995</v>
       </c>
       <c r="B23">
-        <v>-0.79709337078458964</v>
+        <v>-1.1122306852701407</v>
       </c>
       <c r="C23">
         <v>258.22826917492205</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6.9067057087551973</v>
+        <v>6.8084573914809594</v>
       </c>
       <c r="B24">
-        <v>-1.2628733819632139</v>
+        <v>-1.5877032800834205</v>
       </c>
       <c r="C24">
         <v>258.22826917492205</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>8.2356187491222066</v>
+        <v>8.13400155491782</v>
       </c>
       <c r="B25">
-        <v>-1.7347792910115374</v>
+        <v>-2.0685259026317562</v>
       </c>
       <c r="C25">
         <v>258.22826917492205</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>9.562497195172238</v>
+        <v>9.4577045352596656</v>
       </c>
       <c r="B26">
-        <v>-2.212904462457816</v>
+        <v>-2.5547606383640735</v>
       </c>
       <c r="C26">
         <v>258.22826917492205</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>10.887273665202091</v>
+        <v>10.779519743765595</v>
       </c>
       <c r="B27">
-        <v>-2.6974548658605237</v>
+        <v>-3.0465444337576821</v>
       </c>
       <c r="C27">
         <v>258.22826917492205</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>12.209871567993806</v>
+        <v>12.099394224825804</v>
       </c>
       <c r="B28">
-        <v>-3.1886646220356725</v>
+        <v>-3.5440329505469679</v>
       </c>
       <c r="C28">
         <v>258.22826917492205</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>13.53021431232945</v>
+        <v>13.417275022830507</v>
       </c>
       <c r="B29">
-        <v>-3.6867678517992868</v>
+        <v>-4.047381850466329</v>
       </c>
       <c r="C29">
         <v>258.22826917492205</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>14.848267021320158</v>
+        <v>14.733137980948378</v>
       </c>
       <c r="B30">
-        <v>-4.1918711653594327</v>
+        <v>-4.5566621419372861</v>
       </c>
       <c r="C30">
         <v>258.22826917492205</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>16.164161675393366</v>
+        <v>16.047074137461934</v>
       </c>
       <c r="B31">
-        <v>-4.7035711304923717</v>
+        <v>-5.0716062201298611</v>
       </c>
       <c r="C31">
         <v>258.22826917492205</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>17.478071969305628</v>
+        <v>17.359203329432173</v>
       </c>
       <c r="B32">
-        <v>-5.2213368043664206</v>
+        <v>-5.591861826901213</v>
       </c>
       <c r="C32">
         <v>258.22826917492205</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>18.790171597813451</v>
+        <v>18.669645393920078</v>
       </c>
       <c r="B33">
-        <v>-5.744637244149895</v>
+        <v>-6.1170767041084941</v>
       </c>
       <c r="C33">
         <v>258.22826917492205</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>20.100566888781675</v>
+        <v>19.97847363999233</v>
       </c>
       <c r="B34">
-        <v>-6.2731474312943218</v>
+        <v>-6.6470353615229527</v>
       </c>
       <c r="C34">
         <v>258.22826917492205</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>21.409094702508366</v>
+        <v>21.285575264738409</v>
       </c>
       <c r="B35">
-        <v>-6.8073660443841169</v>
+        <v>-7.1820693805722406</v>
       </c>
       <c r="C35">
         <v>258.22826917492205</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>22.715524532399886</v>
+        <v>22.590790937253491</v>
       </c>
       <c r="B36">
-        <v>-7.34799768628691</v>
+        <v>-7.7226471105981025</v>
       </c>
       <c r="C36">
         <v>258.22826917492205</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>24.019625871862633</v>
+        <v>23.893961326632766</v>
       </c>
       <c r="B37">
-        <v>-7.8957469598703431</v>
+        <v>-8.2692369009422961</v>
       </c>
       <c r="C37">
         <v>258.22826917492205</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>25.321002979717488</v>
+        <v>25.194812991799157</v>
       </c>
       <c r="B38">
-        <v>-8.451823550138478</v>
+        <v>-8.8226425250385</v>
       </c>
       <c r="C38">
         <v>258.22826917492205</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>26.618599176443364</v>
+        <v>26.492616050986523</v>
       </c>
       <c r="B39">
-        <v>-9.0194574706411075</v>
+        <v>-9.3850094526881449</v>
       </c>
       <c r="C39">
         <v>258.22826917492205</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>27.911192547933677</v>
+        <v>27.786526512256458</v>
       </c>
       <c r="B40">
-        <v>-9.6023838170644673</v>
+        <v>-9.9588185777845961</v>
       </c>
       <c r="C40">
         <v>258.22826917492205</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>29.197561180081859</v>
+        <v>29.075700383670561</v>
       </c>
       <c r="B41">
-        <v>-10.204337685094775</v>
+        <v>-10.546550794221211</v>
       </c>
       <c r="C41">
         <v>258.22826917492205</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>29.197561180081859</v>
+        <v>29.075700383670561</v>
       </c>
       <c r="B42">
-        <v>-10.204337685094775</v>
+        <v>-10.546550794221211</v>
       </c>
       <c r="C42">
         <v>258.22826917492205</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>27.853478139729187</v>
+        <v>27.746671567285038</v>
       </c>
       <c r="B43">
-        <v>-9.77880279443612</v>
+        <v>-10.07597122474902</v>
       </c>
       <c r="C43">
         <v>258.22826917492205</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>26.513082353193337</v>
+        <v>26.419750932638802</v>
       </c>
       <c r="B44">
-        <v>-9.3419968612785258</v>
+        <v>-9.599194706034579</v>
       </c>
       <c r="C44">
         <v>258.22826917492205</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>25.175153028012904</v>
+        <v>25.094095649629161</v>
       </c>
       <c r="B45">
-        <v>-8.8976515527103963</v>
+        <v>-9.1186987167832978</v>
       </c>
       <c r="C45">
         <v>258.22826917492205</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>23.838469371726497</v>
+        <v>23.768862888153429</v>
       </c>
       <c r="B46">
-        <v>-8.44949853582013</v>
+        <v>-8.6369607357005833</v>
       </c>
       <c r="C46">
         <v>258.22826917492205</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>22.501975787742804</v>
+        <v>22.443323888178529</v>
       </c>
       <c r="B47">
-        <v>-8.0007645139033219</v>
+        <v>-8.1561229352806777</v>
       </c>
       <c r="C47">
         <v>258.22826917492205</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>21.165277462950833</v>
+        <v>21.117206169949824</v>
       </c>
       <c r="B48">
-        <v>-7.55265633508441</v>
+        <v>-7.6769862631731893</v>
       </c>
       <c r="C48">
         <v>258.22826917492205</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>19.82814478010966</v>
+        <v>19.790351323782275</v>
       </c>
       <c r="B49">
-        <v>-7.1058758836950195</v>
+        <v>-7.2000163608165533</v>
       </c>
       <c r="C49">
         <v>258.22826917492205</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>18.490348121978386</v>
+        <v>18.46260093999086</v>
       </c>
       <c r="B50">
-        <v>-6.6611250440667868</v>
+        <v>-6.7256788696492134</v>
       </c>
       <c r="C50">
         <v>258.22826917492205</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>17.151725194861115</v>
+        <v>17.13384309198501</v>
       </c>
       <c r="B51">
-        <v>-6.2188999087483907</v>
+        <v>-6.2543027951775434</v>
       </c>
       <c r="C51">
         <v>258.22826917492205</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>15.812382999242088</v>
+        <v>15.804151785551936</v>
       </c>
       <c r="B52">
-        <v>-5.7788734031566911</v>
+        <v>-5.7856705991796487</v>
       </c>
       <c r="C52">
         <v>258.22826917492205</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>14.472495859150556</v>
+        <v>14.47364750957331</v>
       </c>
       <c r="B53">
-        <v>-5.3405126609255857</v>
+        <v>-5.3194281075015661</v>
       </c>
       <c r="C53">
         <v>258.22826917492205</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>13.132238098615746</v>
+        <v>13.142450752930779</v>
       </c>
       <c r="B54">
-        <v>-4.9032848156889708</v>
+        <v>-4.8552211459893257</v>
       </c>
       <c r="C54">
         <v>258.22826917492205</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>11.791742285402378</v>
+        <v>11.810653162289457</v>
       </c>
       <c r="B55">
-        <v>-4.4667846398752813</v>
+        <v>-4.3927803214870567</v>
       </c>
       <c r="C55">
         <v>258.22826917492205</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>10.450973962216962</v>
+        <v>10.478231015448243</v>
       </c>
       <c r="B56">
-        <v>-4.0311174610910623</v>
+        <v>-3.9321753648312474</v>
       </c>
       <c r="C56">
         <v>258.22826917492205</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>9.1098569155014637</v>
+        <v>9.145131747989474</v>
       </c>
       <c r="B57">
-        <v>-3.5965162457373867</v>
+        <v>-3.4735607878564747</v>
       </c>
       <c r="C57">
         <v>258.22826917492205</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>7.7683149316978692</v>
+        <v>7.8113027954955108</v>
       </c>
       <c r="B58">
-        <v>-3.1632139602153386</v>
+        <v>-3.0170911023973255</v>
       </c>
       <c r="C58">
         <v>258.22826917492205</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>6.4262809650750139</v>
+        <v>6.476697917235966</v>
       </c>
       <c r="B59">
-        <v>-2.7314155470980777</v>
+        <v>-2.5629022319625192</v>
       </c>
       <c r="C59">
         <v>258.22826917492205</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5.0837246412092885</v>
+        <v>5.1412961672296085</v>
       </c>
       <c r="B60">
-        <v>-2.3012138536471296</v>
+        <v>-2.1110557467573785</v>
       </c>
       <c r="C60">
         <v>258.22826917492205</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.7406247535039605</v>
+        <v>3.8050829231824856</v>
       </c>
       <c r="B61">
-        <v>-1.8726737032961045</v>
+        <v>-1.6615946286613692</v>
       </c>
       <c r="C61">
         <v>258.22826917492205</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.3969600953623051</v>
+        <v>2.4680435628006543</v>
       </c>
       <c r="B62">
-        <v>-1.4458599194786177</v>
+        <v>-1.2145618595539622</v>
       </c>
       <c r="C62">
         <v>258.22826917492205</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.0527653759743207</v>
+        <v>1.1302020692076278</v>
       </c>
       <c r="B63">
-        <v>-1.0206664046014464</v>
+        <v>-0.76988694162355109</v>
       </c>
       <c r="C63">
         <v>258.22826917492205</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.29170103232309286</v>
+        <v>-0.20826315280323235</v>
       </c>
       <c r="B64">
-        <v>-0.59630337696402336</v>
+        <v>-0.3270454582942342</v>
       </c>
       <c r="C64">
         <v>258.22826917492205</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.6361248414062843</v>
+        <v>-1.5471350930210781</v>
       </c>
       <c r="B65">
-        <v>-0.17181013383895233</v>
+        <v>0.11460048670095582</v>
       </c>
       <c r="C65">
         <v>258.22826917492205</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.980191763151625</v>
+        <v>-2.8861967412350844</v>
       </c>
       <c r="B66">
-        <v>0.25377402750116956</v>
+        <v>0.555688789628994</v>
       </c>
       <c r="C66">
         <v>258.22826917492205</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.32399355418007</v>
+        <v>-4.2255114892755472</v>
       </c>
       <c r="B67">
-        <v>0.68016862927376653</v>
+        <v>0.99603311173767539</v>
       </c>
       <c r="C67">
         <v>258.22826917492205</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.6692461500909337</v>
+        <v>-5.566264337137282</v>
       </c>
       <c r="B68">
-        <v>1.1021284716563571</v>
+        <v>1.4321501741980827</v>
       </c>
       <c r="C68">
         <v>258.22826917492205</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-7.0172785850058821</v>
+        <v>-6.909373116923434</v>
       </c>
       <c r="B69">
-        <v>1.5155910190026671</v>
+        <v>1.8613420317382239</v>
       </c>
       <c r="C69">
         <v>258.22826917492205</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-8.3662481081575191</v>
+        <v>-8.2535653810058562</v>
       </c>
       <c r="B70">
-        <v>1.9261891144111205</v>
+        <v>2.287349013390481</v>
       </c>
       <c r="C70">
         <v>258.22826917492205</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-9.7141456046864025</v>
+        <v>-9.5974538048337479</v>
       </c>
       <c r="B71">
-        <v>2.3400641357447522</v>
+        <v>2.7142491261234136</v>
       </c>
       <c r="C71">
         <v>258.22826917492205</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-11.061468288253938</v>
+        <v>-10.941381835896966</v>
       </c>
       <c r="B72">
-        <v>2.7556962211803335</v>
+        <v>3.1410328143458943</v>
       </c>
       <c r="C72">
         <v>258.22826917492205</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-12.409046851995907</v>
+        <v>-12.285923214916791</v>
       </c>
       <c r="B73">
-        <v>3.1705461428528552</v>
+        <v>3.5660135810820113</v>
       </c>
       <c r="C73">
         <v>258.22826917492205</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-13.756539578424784</v>
+        <v>-13.630842083499548</v>
       </c>
       <c r="B74">
-        <v>3.58565844841645</v>
+        <v>3.9898847263764008</v>
       </c>
       <c r="C74">
         <v>258.22826917492205</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-15.103305232807374</v>
+        <v>-14.9756957574881</v>
       </c>
       <c r="B75">
-        <v>4.00299323725368</v>
+        <v>4.4139475096039122</v>
       </c>
       <c r="C75">
         <v>258.22826917492205</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-16.448676922051096</v>
+        <v>-16.320023848786388</v>
       </c>
       <c r="B76">
-        <v>4.4245890401416688</v>
+        <v>4.8395552304397285</v>
       </c>
       <c r="C76">
         <v>258.22826917492205</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-17.792037159933145</v>
+        <v>-17.663400094857703</v>
       </c>
       <c r="B77">
-        <v>4.8523333630145142</v>
+        <v>5.2679608773025519</v>
       </c>
       <c r="C77">
         <v>258.22826917492205</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-19.132991746069148</v>
+        <v>-19.005552439341642</v>
       </c>
       <c r="B78">
-        <v>5.2874311810396488</v>
+        <v>5.6999641532848626</v>
       </c>
       <c r="C78">
         <v>258.22826917492205</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-20.470868988029853</v>
+        <v>-20.346017209332185</v>
       </c>
       <c r="B79">
-        <v>5.73193569540487</v>
+        <v>6.1369280136813043</v>
       </c>
       <c r="C79">
         <v>258.22826917492205</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-21.804490785786406</v>
+        <v>-21.683981043422957</v>
       </c>
       <c r="B80">
-        <v>6.1894480727650389</v>
+        <v>6.5812433146770584</v>
       </c>
       <c r="C80">
         <v>258.22826917492205</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-23.130964659890374</v>
+        <v>-23.017446718195846</v>
       </c>
       <c r="B81">
-        <v>6.6688099227326676</v>
+        <v>7.0387808462124744</v>
       </c>
       <c r="C81">
         <v>258.22826917492205</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-24.398216592835812</v>
+        <v>-24.310454488322321</v>
       </c>
       <c r="B82">
-        <v>7.3291989134470876</v>
+        <v>7.6152434100961033</v>
       </c>
       <c r="C82">
         <v>258.22826917492205</v>
